--- a/docs/dossiers/dossier-paris-12e-1500a262.xlsx
+++ b/docs/dossiers/dossier-paris-12e-1500a262.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-12e-1500a262.xlsx
+++ b/docs/dossiers/dossier-paris-12e-1500a262.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +567 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +615 €/mois.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>3255.33</v>
+        <v>3310.67</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>

--- a/docs/dossiers/dossier-paris-12e-1500a262.xlsx
+++ b/docs/dossiers/dossier-paris-12e-1500a262.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
